--- a/Codes_2025/Trial 3/Trial3_Proposed (Gradient Boost)_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_Proposed (Gradient Boost)_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,14 +478,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>37.81</v>
+        <v>33.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37.22033627553438</v>
+        <v>138.2814749124051</v>
       </c>
       <c r="F2" t="n">
-        <v>73.67257690429688</v>
+        <v>144.8902435302734</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,23 +504,23 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>37.49401248859071</v>
+        <v>39.71996810538776</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3159875114092969</v>
+        <v>5.839968105387761</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>33.88</v>
+        <v>28.09</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>138.2814749124051</v>
+        <v>30.68767035587374</v>
       </c>
       <c r="F3" t="n">
-        <v>111.884147644043</v>
+        <v>44.28973388671875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>39.7565422635879</v>
+        <v>33.72770432808887</v>
       </c>
       <c r="I3" t="n">
-        <v>5.876542263587893</v>
+        <v>5.637704328088873</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>28.09</v>
+        <v>19.89</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30.68767035587374</v>
+        <v>16.07039809120311</v>
       </c>
       <c r="F4" t="n">
-        <v>37.99192047119141</v>
+        <v>19.26447105407715</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,23 +574,23 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>30.51826142537681</v>
+        <v>16.66152847152122</v>
       </c>
       <c r="I4" t="n">
-        <v>2.428261425376814</v>
+        <v>3.228471528478778</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>24.26000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36.70529760187497</v>
+        <v>9.038987214440688</v>
       </c>
       <c r="F5" t="n">
-        <v>30.15367317199707</v>
+        <v>9.071558952331543</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>34.8929379465206</v>
+        <v>9.12447670594648</v>
       </c>
       <c r="I5" t="n">
-        <v>10.6329379465206</v>
+        <v>2.475523294053522</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>19.89</v>
+        <v>10.68</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.07039809120311</v>
+        <v>12.34611016321944</v>
       </c>
       <c r="F6" t="n">
-        <v>21.1674861907959</v>
+        <v>11.78069400787354</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,23 +644,23 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>17.92685266665712</v>
+        <v>15.33256078531776</v>
       </c>
       <c r="I6" t="n">
-        <v>1.963147333342878</v>
+        <v>4.65256078531776</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>11.6</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9.038987214440688</v>
+        <v>47.01637236983374</v>
       </c>
       <c r="F7" t="n">
-        <v>7.994204044342041</v>
+        <v>12.66692161560059</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -679,23 +679,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9.059180907836598</v>
+        <v>25.50731886815329</v>
       </c>
       <c r="I7" t="n">
-        <v>2.540819092163403</v>
+        <v>17.45731886815329</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>10.68</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.34611016321944</v>
+        <v>13.45661751886732</v>
       </c>
       <c r="F8" t="n">
-        <v>11.35935878753662</v>
+        <v>11.50274181365967</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>12.66783660799993</v>
+        <v>15.33256078531776</v>
       </c>
       <c r="I8" t="n">
-        <v>1.987836607999933</v>
+        <v>7.342560785317759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>8.050000000000002</v>
+        <v>7.740000000000002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.01637236983374</v>
+        <v>9.929802182220868</v>
       </c>
       <c r="F9" t="n">
-        <v>9.724125862121582</v>
+        <v>7.620044231414795</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11.51533985106799</v>
+        <v>8.692187307072773</v>
       </c>
       <c r="I9" t="n">
-        <v>3.465339851067986</v>
+        <v>0.9521873070727711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>7.989999999999999</v>
+        <v>5.93</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13.45661751886732</v>
+        <v>7.94460938405617</v>
       </c>
       <c r="F10" t="n">
-        <v>11.40179824829102</v>
+        <v>6.059847831726074</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -784,23 +784,23 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>12.66783660799993</v>
+        <v>6.673635458663234</v>
       </c>
       <c r="I10" t="n">
-        <v>4.677836607999931</v>
+        <v>0.7436354586632348</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.740000000000002</v>
+        <v>5.56</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.929802182220868</v>
+        <v>3.665586355441213</v>
       </c>
       <c r="F11" t="n">
-        <v>8.274786949157715</v>
+        <v>4.010782718658447</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9.183330605079609</v>
+        <v>3.94342520987789</v>
       </c>
       <c r="I11" t="n">
-        <v>1.443330605079607</v>
+        <v>1.616574790122109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.81</v>
+        <v>2.64</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.71820080519103</v>
+        <v>3.577960374161461</v>
       </c>
       <c r="F12" t="n">
-        <v>9.794834136962891</v>
+        <v>3.132464170455933</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -854,115 +854,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>11.36731709863819</v>
+        <v>3.092576502607078</v>
       </c>
       <c r="I12" t="n">
-        <v>4.557317098638191</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>7.94460938405617</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6.411643981933594</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>6.315338455591713</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.3853384555917136</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3.665586355441213</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.699268579483032</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>3.972121221612847</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.587878778387152</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3.577960374161461</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3.355034351348877</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>3.758393769440175</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.118393769440175</v>
+        <v>0.4525765026070774</v>
       </c>
     </row>
   </sheetData>
